--- a/artfynd/A 53829-2024 artfynd.xlsx
+++ b/artfynd/A 53829-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111802077</v>
+        <v>111802034</v>
       </c>
       <c r="B2" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596559</v>
+        <v>596769</v>
       </c>
       <c r="R2" t="n">
-        <v>7074788</v>
+        <v>7074674</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111801895</v>
+        <v>111802039</v>
       </c>
       <c r="B3" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596935</v>
+        <v>596604</v>
       </c>
       <c r="R3" t="n">
-        <v>7074567</v>
+        <v>7074751</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111802034</v>
+        <v>111802070</v>
       </c>
       <c r="B4" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596769</v>
+        <v>596579</v>
       </c>
       <c r="R4" t="n">
-        <v>7074673</v>
+        <v>7074787</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111802039</v>
+        <v>111801875</v>
       </c>
       <c r="B5" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596604</v>
+        <v>596700</v>
       </c>
       <c r="R5" t="n">
-        <v>7074752</v>
+        <v>7075105</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111801887</v>
+        <v>111802085</v>
       </c>
       <c r="B6" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596684</v>
+        <v>596701</v>
       </c>
       <c r="R6" t="n">
-        <v>7074878</v>
+        <v>7074816</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111801875</v>
+        <v>111801871</v>
       </c>
       <c r="B7" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596700</v>
+        <v>596688</v>
       </c>
       <c r="R7" t="n">
-        <v>7075105</v>
+        <v>7075114</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111802085</v>
+        <v>111801887</v>
       </c>
       <c r="B8" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596701</v>
+        <v>596684</v>
       </c>
       <c r="R8" t="n">
-        <v>7074816</v>
+        <v>7074878</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111802086</v>
+        <v>111801938</v>
       </c>
       <c r="B9" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596701</v>
+        <v>596857</v>
       </c>
       <c r="R9" t="n">
-        <v>7074813</v>
+        <v>7074596</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111801871</v>
+        <v>111802077</v>
       </c>
       <c r="B10" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596688</v>
+        <v>596559</v>
       </c>
       <c r="R10" t="n">
-        <v>7075113</v>
+        <v>7074788</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1629,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111801938</v>
+        <v>111802086</v>
       </c>
       <c r="B11" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596857</v>
+        <v>596701</v>
       </c>
       <c r="R11" t="n">
-        <v>7074597</v>
+        <v>7074814</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1732,112 +1682,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>111802070</v>
-      </c>
-      <c r="B12" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Backsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>596579</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7074787</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-08-28</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-08-28</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53829-2024 artfynd.xlsx
+++ b/artfynd/A 53829-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802034</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802039</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111801875</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802085</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111801871</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111801887</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111801938</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802077</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,8 +1732,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802086</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>